--- a/TP3/salidas/tablas/TP3_Metricas_Modelos_Logit.xlsx
+++ b/TP3/salidas/tablas/TP3_Metricas_Modelos_Logit.xlsx
@@ -475,19 +475,19 @@
         <v>0.5</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9331</v>
+        <v>0.9301</v>
       </c>
       <c r="D2" t="n">
-        <v>0.907</v>
+        <v>0.8873</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2812</v>
+        <v>0.2513</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4292</v>
+        <v>0.3917</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8748</v>
+        <v>0.8342000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -500,19 +500,19 @@
         <v>0.5</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9459</v>
+        <v>0.9437</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7388</v>
+        <v>0.7317</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4213</v>
+        <v>0.383</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5366</v>
+        <v>0.5028</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9153</v>
+        <v>0.8895</v>
       </c>
     </row>
   </sheetData>
